--- a/Excel/25-div-26q2.xlsx
+++ b/Excel/25-div-26q2.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_0D3FE602C76B83F6535B8088F0344B8CE4B080B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{162DF256-F600-469E-BE0C-7CE8F309174B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="876" windowWidth="12312" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="11520" windowHeight="9012"/>
   </bookViews>
   <sheets>
     <sheet name="PDATE" sheetId="2" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="59">
   <si>
     <t>name</t>
   </si>
@@ -60,6 +54,141 @@
     <t>actual</t>
   </si>
   <si>
+    <t>3BBIF</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>SYNEX</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>ADVANC</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>NER</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>WHART</t>
+  </si>
+  <si>
+    <t>CPNREIT</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>GVREIT</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>PROSPECT</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>AIMIRT</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>DIF</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>IVL</t>
+  </si>
+  <si>
+    <t>BCH</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>CPF</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>JMT</t>
+  </si>
+  <si>
+    <t>STA</t>
+  </si>
+  <si>
+    <t>TFFIF</t>
+  </si>
+  <si>
+    <t>TOA</t>
+  </si>
+  <si>
+    <t>TVO</t>
+  </si>
+  <si>
+    <t>PTTGC</t>
+  </si>
+  <si>
+    <t>WHAIR</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTT </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>POM</t>
+  </si>
+  <si>
     <t>PTT</t>
   </si>
   <si>
@@ -76,152 +205,52 @@
   </si>
   <si>
     <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>3BBIF</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>SYNEX</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>ADVANC</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>NER</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>WHART</t>
-  </si>
-  <si>
-    <t>CPNREIT</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>GVREIT</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>PROSPECT</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>AIMIRT</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>DIF</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>AH</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>IVL</t>
-  </si>
-  <si>
-    <t>BCH</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>CPF</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>JMT</t>
-  </si>
-  <si>
-    <t>STA</t>
-  </si>
-  <si>
-    <t>TFFIF</t>
-  </si>
-  <si>
-    <t>TOA</t>
-  </si>
-  <si>
-    <t>TVO</t>
-  </si>
-  <si>
-    <t>PTTGC</t>
-  </si>
-  <si>
-    <t>WHAIR</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>2025-09-03</t>
-  </si>
-  <si>
-    <t>POM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="9">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="181" formatCode="0.00000"/>
+    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="26">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,53 +260,355 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -300,62 +631,344 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,20 +1250,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="2"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11" style="17" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11" style="13" customWidth="1"/>
+    <col min="6" max="7" width="10.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -666,7 +1279,7 @@
       <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -681,10 +1294,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C2" s="2">
         <v>120000</v>
@@ -693,15 +1306,15 @@
         <f>B2*C2</f>
         <v>16800</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="15">
         <f>D2*0.9</f>
         <v>15120</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>16</v>
+      <c r="F2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -709,7 +1322,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>0.1</v>
@@ -720,14 +1333,14 @@
       <c r="D3" s="3">
         <v>1750</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="13">
         <v>1575</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>16</v>
+      <c r="F3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -735,7 +1348,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>8.69</v>
@@ -746,14 +1359,14 @@
       <c r="D4" s="3">
         <v>3476</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="13">
         <v>3128.4</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>20</v>
+      <c r="F4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -761,7 +1374,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
         <v>0.05</v>
@@ -772,15 +1385,15 @@
       <c r="D5" s="3">
         <v>1350</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="13">
         <f>D5</f>
         <v>1350</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>23</v>
+      <c r="F5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -788,7 +1401,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
         <v>0.5</v>
@@ -799,15 +1412,15 @@
       <c r="D6" s="3">
         <v>12000</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="13">
         <f>D6</f>
         <v>12000</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>23</v>
+      <c r="F6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -815,7 +1428,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
         <v>0.193</v>
@@ -826,14 +1439,14 @@
       <c r="D7" s="3">
         <v>3860</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="13">
         <v>3474</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>23</v>
+      <c r="F7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -841,10 +1454,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C8" s="2">
         <v>55000</v>
@@ -852,14 +1465,14 @@
       <c r="D8" s="3">
         <v>15400</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="13">
         <v>13860</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>28</v>
+      <c r="F8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -867,7 +1480,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1">
         <v>0.1875</v>
@@ -879,15 +1492,15 @@
         <f>B9*C9</f>
         <v>12937.5</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="13">
         <f>D9*0.9</f>
         <v>11643.75</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>28</v>
+      <c r="F9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -895,10 +1508,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1">
-        <v>7.0499999999999993E-2</v>
+        <v>0.0705</v>
       </c>
       <c r="C10" s="2">
         <v>30000</v>
@@ -907,15 +1520,15 @@
         <f>B10*C10</f>
         <v>2115</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="13">
         <f>D10*0.9</f>
         <v>1903.5</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>28</v>
+      <c r="F10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -923,10 +1536,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="C11" s="2">
         <v>10000</v>
@@ -934,14 +1547,14 @@
       <c r="D11" s="3">
         <v>2050</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="13">
         <v>1845</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>34</v>
+      <c r="F11" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>28</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -949,10 +1562,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="C12" s="2">
         <v>45000</v>
@@ -960,14 +1573,14 @@
       <c r="D12" s="3">
         <v>9999</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="13">
         <v>8999.1</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>34</v>
+      <c r="F12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>28</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -975,7 +1588,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1">
         <v>0.38</v>
@@ -986,14 +1599,14 @@
       <c r="D13" s="3">
         <v>456</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="13">
         <v>410.4</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>39</v>
+      <c r="F13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1001,7 +1614,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -1013,7 +1626,7 @@
         <f>B14*C14</f>
         <v>1440</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="13">
         <f>D14*0.9</f>
         <v>1296</v>
       </c>
@@ -1029,7 +1642,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1">
         <v>0.35</v>
@@ -1040,14 +1653,14 @@
       <c r="D15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="13">
         <v>1260</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1055,7 +1668,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1">
         <v>0.45</v>
@@ -1066,14 +1679,14 @@
       <c r="D16" s="3">
         <v>4500</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="13">
         <v>4050</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1081,7 +1694,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1">
         <v>0.27</v>
@@ -1092,14 +1705,14 @@
       <c r="D17" s="3">
         <v>1890</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="13">
         <v>1701</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1107,7 +1720,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>0.5</v>
@@ -1119,7 +1732,7 @@
         <f>B18*C18</f>
         <v>5000</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="13">
         <f>D18*0.9</f>
         <v>4500</v>
       </c>
@@ -1135,7 +1748,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" s="12">
         <v>0.1133</v>
@@ -1144,18 +1757,18 @@
         <v>25000</v>
       </c>
       <c r="D19" s="3">
-        <f>B19*C19</f>
+        <f t="shared" ref="D19:D24" si="0">B19*C19</f>
         <v>2832.5</v>
       </c>
-      <c r="E19" s="17">
-        <f>D19*0.9</f>
+      <c r="E19" s="13">
+        <f t="shared" ref="E19:E24" si="1">D19*0.9</f>
         <v>2549.25</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1163,7 +1776,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1">
         <v>0.38</v>
@@ -1174,14 +1787,14 @@
       <c r="D20" s="3">
         <v>380</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="13">
         <v>342</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>38</v>
+      <c r="F20" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1189,7 +1802,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>0.9</v>
@@ -1200,14 +1813,14 @@
       <c r="D21" s="3">
         <v>3600</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="13">
         <v>3472</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>38</v>
+      <c r="F21" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1215,7 +1828,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1">
         <v>0.6</v>
@@ -1224,11 +1837,11 @@
         <v>6000</v>
       </c>
       <c r="D22" s="3">
-        <f>B22*C22</f>
+        <f t="shared" si="0"/>
         <v>3600</v>
       </c>
-      <c r="E22" s="17">
-        <f>D22*0.9</f>
+      <c r="E22" s="13">
+        <f t="shared" si="1"/>
         <v>3240</v>
       </c>
       <c r="F22" s="10">
@@ -1243,7 +1856,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1">
         <v>0.1434</v>
@@ -1254,14 +1867,14 @@
       <c r="D23" s="3">
         <v>7170</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="13">
         <v>6453</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>30</v>
+      <c r="F23" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1269,20 +1882,20 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C24" s="2">
         <v>30000</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" ref="D19:D24" si="0">B24*C24</f>
+        <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="E24" s="17">
-        <f t="shared" ref="E19:E24" si="1">D24*0.9</f>
+      <c r="E24" s="13">
+        <f t="shared" si="1"/>
         <v>3780</v>
       </c>
       <c r="F24" s="4">
@@ -1296,67 +1909,66 @@
       </c>
     </row>
     <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>7500</v>
+      </c>
       <c r="D25" s="3">
-        <f>SUM(D2:D24)</f>
-        <v>118206</v>
-      </c>
-      <c r="E25" s="17">
-        <f>SUM(E2:E24)</f>
-        <v>107952.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="C26" s="2">
-        <v>30000</v>
-      </c>
+        <f>B25*C25</f>
+        <v>10500</v>
+      </c>
+      <c r="E25" s="13">
+        <f>D25*0.9</f>
+        <v>9450</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46302</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46317</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5">
       <c r="D26" s="3">
-        <f>B26*C26</f>
-        <v>4200</v>
-      </c>
-      <c r="E26" s="17">
-        <f>D26*0.9</f>
-        <v>3780</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
+        <f>SUM(D2:D25)</f>
+        <v>128706</v>
+      </c>
+      <c r="E26" s="13">
+        <f>SUM(E2:E25)</f>
+        <v>117402.4</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>54</v>
+        <v>8</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.14</v>
       </c>
       <c r="C27" s="2">
-        <f>C3+C26</f>
-        <v>47500</v>
-      </c>
-      <c r="D27" s="15">
-        <f>D3+D26</f>
-        <v>5950</v>
-      </c>
-      <c r="E27" s="18">
-        <f>E3+E26</f>
-        <v>5355</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" t="s">
-        <v>56</v>
+        <v>30000</v>
+      </c>
+      <c r="D27" s="3">
+        <f>B27*C27</f>
+        <v>4200</v>
+      </c>
+      <c r="E27" s="13">
+        <f>D27*0.9</f>
+        <v>3780</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1364,27 +1976,28 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.28000000000000003</v>
+        <v>48</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>55000</v>
-      </c>
-      <c r="D28" s="3">
-        <f>B28*C28</f>
-        <v>15400.000000000002</v>
-      </c>
-      <c r="E28" s="17">
-        <f>D28*0.9</f>
-        <v>13860.000000000002</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>25</v>
+        <f>C3+C27</f>
+        <v>47500</v>
+      </c>
+      <c r="D28" s="18">
+        <f>D3+D27</f>
+        <v>5950</v>
+      </c>
+      <c r="E28" s="19">
+        <f>E3+E27</f>
+        <v>5355</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1392,64 +2005,94 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C29" s="2">
-        <v>24000</v>
+        <v>55000</v>
       </c>
       <c r="D29" s="3">
         <f>B29*C29</f>
-        <v>6720.0000000000009</v>
-      </c>
-      <c r="E29" s="17">
+        <v>15400</v>
+      </c>
+      <c r="E29" s="13">
         <f>D29*0.9</f>
-        <v>6048.0000000000009</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>25</v>
+        <v>13860</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="B30"/>
-      <c r="E30" s="17">
-        <f>E28+E29</f>
-        <v>19908.000000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.28</v>
+      </c>
+      <c r="C30" s="2">
+        <v>24000</v>
+      </c>
+      <c r="D30" s="3">
+        <f>B30*C30</f>
+        <v>6720</v>
+      </c>
+      <c r="E30" s="13">
+        <f>D30*0.9</f>
+        <v>6048</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
       <c r="B31"/>
+      <c r="E31" s="13">
+        <f>E29+E30</f>
+        <v>19908</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H23">
+  <sortState ref="A2:H23">
     <sortCondition ref="G2:G23"/>
     <sortCondition ref="A2:A23"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D25" formula="1"/>
+    <ignoredError sqref="D26" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="2"/>
     <col min="4" max="5" width="11" style="3" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" style="4" customWidth="1"/>
+    <col min="6" max="7" width="10.3333333333333" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1480,7 +2123,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B2" s="1">
         <v>0.9</v>
@@ -1495,10 +2138,10 @@
         <v>6075</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1506,7 +2149,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>0.25</v>
@@ -1521,10 +2164,10 @@
         <v>16875</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1532,10 +2175,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="C4" s="2">
         <v>45000</v>
@@ -1547,10 +2190,10 @@
         <v>8999.1</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1558,10 +2201,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C5" s="2">
         <v>120000</v>
@@ -1573,10 +2216,10 @@
         <v>15120</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1584,7 +2227,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
         <v>8.69</v>
@@ -1599,10 +2242,10 @@
         <v>3128.4</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1610,7 +2253,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1">
         <v>0.1</v>
@@ -1625,10 +2268,10 @@
         <v>1575</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1636,7 +2279,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1">
         <v>0.193</v>
@@ -1651,10 +2294,10 @@
         <v>3474</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1662,7 +2305,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
         <v>0.05</v>
@@ -1678,10 +2321,10 @@
         <v>1350</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1689,10 +2332,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="C10" s="2">
         <v>10000</v>
@@ -1704,10 +2347,10 @@
         <v>1845</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1715,10 +2358,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C11" s="2">
         <v>55000</v>
@@ -1730,10 +2373,10 @@
         <v>13860</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1741,7 +2384,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1">
         <v>0.5</v>
@@ -1757,10 +2400,10 @@
         <v>12000</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1768,7 +2411,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>0.27</v>
@@ -1783,10 +2426,10 @@
         <v>1701</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1794,10 +2437,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
-        <v>7.0499999999999993E-2</v>
+        <v>0.0705</v>
       </c>
       <c r="C14" s="2">
         <v>30000</v>
@@ -1811,10 +2454,10 @@
         <v>1903.5</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1822,7 +2465,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1">
         <v>0.1875</v>
@@ -1839,10 +2482,10 @@
         <v>11643.75</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1850,7 +2493,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" s="12">
         <v>0.1133</v>
@@ -1867,10 +2510,10 @@
         <v>2549.25</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1878,7 +2521,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1">
         <v>0.1434</v>
@@ -1893,10 +2536,10 @@
         <v>6453</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1904,7 +2547,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1">
         <v>0.38</v>
@@ -1919,10 +2562,10 @@
         <v>410.4</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1930,7 +2573,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1">
         <v>0.35</v>
@@ -1945,10 +2588,10 @@
         <v>1260</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1956,7 +2599,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1">
         <v>0.2</v>
@@ -1984,7 +2627,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1">
         <v>0.5</v>
@@ -2012,7 +2655,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1">
         <v>0.38</v>
@@ -2027,10 +2670,10 @@
         <v>342</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2038,7 +2681,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1">
         <v>0.9</v>
@@ -2053,10 +2696,10 @@
         <v>3472</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -2064,7 +2707,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1">
         <v>0.45</v>
@@ -2079,10 +2722,10 @@
         <v>4050</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2090,7 +2733,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1">
         <v>0.6</v>
@@ -2118,10 +2761,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C26" s="2">
         <v>30000</v>
@@ -2144,22 +2787,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="4:5">
       <c r="D27" s="3">
         <f>SUM(D2:D26)</f>
         <v>143706</v>
       </c>
       <c r="E27" s="3">
         <f>SUM(E2:E26)</f>
-        <v>130902.39999999999</v>
+        <v>130902.4</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H25">
+  <sortState ref="A2:H25">
     <sortCondition ref="F2:F25"/>
     <sortCondition ref="A2:A25"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/25-div-26q2.xlsx
+++ b/Excel/25-div-26q2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_0C3FE602B81344983FFD989F30865698DA6EAA1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{809EBB6E-5265-4051-98B4-B22E0911A08D}"/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9012"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="10056" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PDATE" sheetId="2" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
   <si>
     <t>name</t>
   </si>
@@ -187,42 +193,20 @@
   </si>
   <si>
     <t>POM</t>
-  </si>
-  <si>
-    <t>PTT</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>MCS</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.0000"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="0.00000"/>
-    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,345 +254,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -631,344 +293,63 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1250,20 +631,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="8.88888888888889" style="1"/>
-    <col min="3" max="3" width="8.88888888888889" style="2"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="8.88671875" style="2"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
     <col min="5" max="5" width="11" style="13" customWidth="1"/>
-    <col min="6" max="7" width="10.3333333333333" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1297,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C2" s="2">
         <v>120000</v>
@@ -1457,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C8" s="2">
         <v>55000</v>
@@ -1511,7 +892,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="1">
-        <v>0.0705</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="C10" s="2">
         <v>30000</v>
@@ -1539,7 +920,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="1">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="C11" s="2">
         <v>10000</v>
@@ -1565,7 +946,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>0.2222</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="C12" s="2">
         <v>45000</v>
@@ -1885,7 +1266,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C24" s="2">
         <v>30000</v>
@@ -1898,10 +1279,10 @@
         <f t="shared" si="1"/>
         <v>3780</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="20">
         <v>46290</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="20">
         <v>46307</v>
       </c>
       <c r="H24">
@@ -1936,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="4:5">
+    <row r="26" spans="1:8">
       <c r="D26" s="3">
         <f>SUM(D2:D25)</f>
         <v>128706</v>
@@ -1951,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C27" s="2">
         <v>30000</v>
@@ -2008,7 +1389,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C29" s="2">
         <v>55000</v>
@@ -2036,7 +1417,7 @@
         <v>52</v>
       </c>
       <c r="B30" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C30" s="2">
         <v>24000</v>
@@ -2059,24 +1440,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:5">
+    <row r="31" spans="1:8">
       <c r="B31"/>
       <c r="E31" s="13">
         <f>E29+E30</f>
         <v>19908</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="1:8">
       <c r="B32"/>
     </row>
   </sheetData>
-  <sortState ref="A2:H23">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H23">
     <sortCondition ref="G2:G23"/>
     <sortCondition ref="A2:A23"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
   <ignoredErrors>
     <ignoredError sqref="D26" formula="1"/>
   </ignoredErrors>
@@ -2084,15 +1464,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="8.88888888888889" style="1"/>
-    <col min="3" max="3" width="8.88888888888889" style="2"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="8.88671875" style="2"/>
     <col min="4" max="5" width="11" style="3" customWidth="1"/>
-    <col min="6" max="7" width="10.3333333333333" style="4" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2123,77 +1502,77 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.9</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C2" s="2">
-        <v>7500</v>
+        <v>120000</v>
       </c>
       <c r="D2" s="3">
-        <v>6750</v>
+        <v>16800</v>
       </c>
       <c r="E2" s="3">
-        <v>6075</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>54</v>
+        <v>15120</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>0.25</v>
+        <v>8.69</v>
       </c>
       <c r="C3" s="2">
-        <v>75000</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3">
-        <v>18750</v>
-      </c>
-      <c r="E3" s="3">
-        <v>16875</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>58</v>
+        <v>3476</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3128.4</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1">
-        <v>0.2222</v>
+        <v>0.38</v>
       </c>
       <c r="C4" s="2">
-        <v>45000</v>
+        <v>1200</v>
       </c>
       <c r="D4" s="3">
-        <v>9999</v>
+        <v>456</v>
       </c>
       <c r="E4" s="3">
-        <v>8999.1</v>
+        <v>410.4</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -2201,25 +1580,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
-        <v>0.14</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="C5" s="2">
-        <v>120000</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="3">
-        <v>16800</v>
+        <v>2050</v>
       </c>
       <c r="E5" s="3">
-        <v>15120</v>
+        <v>1845</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -2227,25 +1606,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1">
-        <v>8.69</v>
+        <v>0.35</v>
       </c>
       <c r="C6" s="2">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="D6" s="3">
-        <v>3476</v>
-      </c>
-      <c r="E6" s="11">
-        <v>3128.4</v>
+        <v>1400</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1260</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2253,25 +1632,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C7" s="2">
-        <v>17500</v>
+        <v>10000</v>
       </c>
       <c r="D7" s="3">
-        <v>1750</v>
+        <v>4500</v>
       </c>
       <c r="E7" s="3">
-        <v>1575</v>
+        <v>4050</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2279,25 +1658,25 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.193</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C8" s="2">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="D8" s="3">
-        <v>3860</v>
-      </c>
-      <c r="E8" s="11">
-        <v>3474</v>
+        <v>15400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13860</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2305,26 +1684,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
-        <v>0.05</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="C9" s="2">
-        <v>27000</v>
+        <v>45000</v>
       </c>
       <c r="D9" s="3">
-        <v>1350</v>
-      </c>
-      <c r="E9" s="11">
-        <f>D9</f>
-        <v>1350</v>
+        <v>9999</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8999.1</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2332,25 +1710,27 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
-        <v>0.205</v>
+        <v>0.1875</v>
       </c>
       <c r="C10" s="2">
-        <v>10000</v>
+        <v>69000</v>
       </c>
       <c r="D10" s="3">
-        <v>2050</v>
+        <f>B10*C10</f>
+        <v>12937.5</v>
       </c>
       <c r="E10" s="3">
-        <v>1845</v>
+        <f>D10*0.9</f>
+        <v>11643.75</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2358,25 +1738,27 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="C11" s="2">
-        <v>55000</v>
+        <v>7200</v>
       </c>
       <c r="D11" s="3">
-        <v>15400</v>
+        <f>B11*C11</f>
+        <v>1440</v>
       </c>
       <c r="E11" s="3">
-        <v>13860</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>22</v>
+        <f>D11*0.9</f>
+        <v>1296</v>
+      </c>
+      <c r="F11" s="10">
+        <v>46261</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46275</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2384,26 +1766,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="C12" s="2">
-        <v>24000</v>
+        <v>7000</v>
       </c>
       <c r="D12" s="3">
-        <v>12000</v>
-      </c>
-      <c r="E12" s="11">
-        <f>D12</f>
-        <v>12000</v>
+        <v>1890</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1701</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2411,25 +1792,26 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="C13" s="2">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="D13" s="3">
-        <v>1890</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1701</v>
+        <v>1350</v>
+      </c>
+      <c r="E13" s="11">
+        <f>D13</f>
+        <v>1350</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -2440,7 +1822,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="1">
-        <v>0.0705</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="C14" s="2">
         <v>30000</v>
@@ -2465,27 +1847,27 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1">
-        <v>0.1875</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C15" s="2">
-        <v>69000</v>
+        <v>30000</v>
       </c>
       <c r="D15" s="3">
         <f>B15*C15</f>
-        <v>12937.5</v>
+        <v>4200</v>
       </c>
       <c r="E15" s="3">
         <f>D15*0.9</f>
-        <v>11643.75</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
+        <v>3780</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46290</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46307</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -2493,27 +1875,27 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="12">
-        <v>0.1133</v>
+        <v>47</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1.4</v>
       </c>
       <c r="C16" s="2">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="D16" s="3">
         <f>B16*C16</f>
-        <v>2832.5</v>
-      </c>
-      <c r="E16" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E16" s="13">
         <f>D16*0.9</f>
-        <v>2549.25</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>36</v>
+        <v>9450</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46302</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46317</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2521,25 +1903,27 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1">
-        <v>0.1434</v>
+        <v>0.6</v>
       </c>
       <c r="C17" s="2">
-        <v>50000</v>
+        <v>6000</v>
       </c>
       <c r="D17" s="3">
-        <v>7170</v>
+        <f>B17*C17</f>
+        <v>3600</v>
       </c>
       <c r="E17" s="3">
-        <v>6453</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>46</v>
+        <f>D17*0.9</f>
+        <v>3240</v>
+      </c>
+      <c r="F17" s="10">
+        <v>46272</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46287</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -2547,25 +1931,26 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="2">
-        <v>1200</v>
+        <v>24000</v>
       </c>
       <c r="D18" s="3">
-        <v>456</v>
-      </c>
-      <c r="E18" s="3">
-        <v>410.4</v>
+        <v>12000</v>
+      </c>
+      <c r="E18" s="11">
+        <f>D18</f>
+        <v>12000</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2573,25 +1958,27 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="C19" s="2">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="D19" s="3">
-        <v>1400</v>
+        <f>B19*C19</f>
+        <v>5000</v>
       </c>
       <c r="E19" s="3">
-        <v>1260</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>36</v>
+        <f>D19*0.9</f>
+        <v>4500</v>
+      </c>
+      <c r="F19" s="10">
+        <v>46261</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46276</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -2599,27 +1986,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C20" s="2">
-        <v>7200</v>
+        <v>17500</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" ref="D20:D26" si="0">B20*C20</f>
-        <v>1440</v>
+        <v>1750</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" ref="E20:E26" si="1">D20*0.9</f>
-        <v>1296</v>
-      </c>
-      <c r="F20" s="10">
-        <v>46261</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46275</v>
+        <v>1575</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -2627,27 +2012,27 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.5</v>
+        <v>41</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.1133</v>
       </c>
       <c r="C21" s="2">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="0"/>
-        <v>5000</v>
+        <f>B21*C21</f>
+        <v>2832.5</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="1"/>
-        <v>4500</v>
-      </c>
-      <c r="F21" s="10">
-        <v>46261</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46276</v>
+        <f>D21*0.9</f>
+        <v>2549.25</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -2707,25 +2092,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" s="1">
-        <v>0.45</v>
+        <v>0.1434</v>
       </c>
       <c r="C24" s="2">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="D24" s="3">
-        <v>4500</v>
+        <v>7170</v>
       </c>
       <c r="E24" s="3">
-        <v>4050</v>
+        <v>6453</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2733,77 +2118,45 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B25" s="1">
-        <v>0.6</v>
+        <v>0.193</v>
       </c>
       <c r="C25" s="2">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="0"/>
-        <v>3600</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="1"/>
-        <v>3240</v>
-      </c>
-      <c r="F25" s="10">
-        <v>46272</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46287</v>
+        <v>3860</v>
+      </c>
+      <c r="E25" s="11">
+        <v>3474</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>30000</v>
-      </c>
       <c r="D26" s="3">
-        <f t="shared" si="0"/>
-        <v>4200</v>
+        <f>SUM(D2:D25)</f>
+        <v>128706</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="1"/>
-        <v>3780</v>
-      </c>
-      <c r="F26" s="4">
-        <v>46290</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46307</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5">
-      <c r="D27" s="3">
-        <f>SUM(D2:D26)</f>
-        <v>143706</v>
-      </c>
-      <c r="E27" s="3">
-        <f>SUM(E2:E26)</f>
-        <v>130902.4</v>
+        <f>SUM(E2:E25)</f>
+        <v>117402.4</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H25">
-    <sortCondition ref="F2:F25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H25">
     <sortCondition ref="A2:A25"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Excel/25-div-26q2.xlsx
+++ b/Excel/25-div-26q2.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0C3FE602B81344983FFD989F30865698DA6EAA1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{809EBB6E-5265-4051-98B4-B22E0911A08D}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="10056" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14688" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="PDATE" sheetId="2" r:id="rId1"/>
@@ -198,15 +192,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="9">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="181" formatCode="0.00000"/>
+    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,13 +235,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -258,19 +249,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -293,63 +614,346 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -631,20 +1235,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="2"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11" style="13" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11" style="12" customWidth="1"/>
+    <col min="6" max="7" width="10.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -678,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C2" s="2">
         <v>120000</v>
@@ -714,7 +1318,7 @@
       <c r="D3" s="3">
         <v>1750</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>1575</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -740,7 +1344,7 @@
       <c r="D4" s="3">
         <v>3476</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>3128.4</v>
       </c>
       <c r="F4" s="16" t="s">
@@ -766,7 +1370,7 @@
       <c r="D5" s="3">
         <v>1350</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>D5</f>
         <v>1350</v>
       </c>
@@ -793,7 +1397,7 @@
       <c r="D6" s="3">
         <v>12000</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>D6</f>
         <v>12000</v>
       </c>
@@ -820,7 +1424,7 @@
       <c r="D7" s="3">
         <v>3860</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>3474</v>
       </c>
       <c r="F7" s="16" t="s">
@@ -838,7 +1442,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C8" s="2">
         <v>55000</v>
@@ -846,7 +1450,7 @@
       <c r="D8" s="3">
         <v>15400</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>13860</v>
       </c>
       <c r="F8" s="16" t="s">
@@ -873,7 +1477,7 @@
         <f>B9*C9</f>
         <v>12937.5</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f>D9*0.9</f>
         <v>11643.75</v>
       </c>
@@ -892,7 +1496,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="1">
-        <v>7.0499999999999993E-2</v>
+        <v>0.0705</v>
       </c>
       <c r="C10" s="2">
         <v>30000</v>
@@ -901,7 +1505,7 @@
         <f>B10*C10</f>
         <v>2115</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f>D10*0.9</f>
         <v>1903.5</v>
       </c>
@@ -920,7 +1524,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="C11" s="2">
         <v>10000</v>
@@ -928,7 +1532,7 @@
       <c r="D11" s="3">
         <v>2050</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>1845</v>
       </c>
       <c r="F11" s="16" t="s">
@@ -946,7 +1550,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="C12" s="2">
         <v>45000</v>
@@ -954,7 +1558,7 @@
       <c r="D12" s="3">
         <v>9999</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>8999.1</v>
       </c>
       <c r="F12" s="16" t="s">
@@ -980,7 +1584,7 @@
       <c r="D13" s="3">
         <v>456</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>410.4</v>
       </c>
       <c r="F13" s="16" t="s">
@@ -1007,7 +1611,7 @@
         <f>B14*C14</f>
         <v>1440</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <f>D14*0.9</f>
         <v>1296</v>
       </c>
@@ -1034,7 +1638,7 @@
       <c r="D15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>1260</v>
       </c>
       <c r="F15" s="10" t="s">
@@ -1060,7 +1664,7 @@
       <c r="D16" s="3">
         <v>4500</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>4050</v>
       </c>
       <c r="F16" s="10" t="s">
@@ -1086,7 +1690,7 @@
       <c r="D17" s="3">
         <v>1890</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>1701</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -1113,7 +1717,7 @@
         <f>B18*C18</f>
         <v>5000</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f>D18*0.9</f>
         <v>4500</v>
       </c>
@@ -1131,18 +1735,18 @@
       <c r="A19" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <v>0.1133</v>
       </c>
       <c r="C19" s="2">
         <v>25000</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" ref="D19:D24" si="0">B19*C19</f>
+        <f t="shared" ref="D19:D25" si="0">B19*C19</f>
         <v>2832.5</v>
       </c>
-      <c r="E19" s="13">
-        <f t="shared" ref="E19:E24" si="1">D19*0.9</f>
+      <c r="E19" s="12">
+        <f t="shared" ref="E19:E25" si="1">D19*0.9</f>
         <v>2549.25</v>
       </c>
       <c r="F19" s="10" t="s">
@@ -1168,7 +1772,7 @@
       <c r="D20" s="3">
         <v>380</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>342</v>
       </c>
       <c r="F20" s="16" t="s">
@@ -1194,7 +1798,7 @@
       <c r="D21" s="3">
         <v>3600</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>3472</v>
       </c>
       <c r="F21" s="16" t="s">
@@ -1221,7 +1825,7 @@
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <f t="shared" si="1"/>
         <v>3240</v>
       </c>
@@ -1248,7 +1852,7 @@
       <c r="D23" s="3">
         <v>7170</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <v>6453</v>
       </c>
       <c r="F23" s="16" t="s">
@@ -1266,7 +1870,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C24" s="2">
         <v>30000</v>
@@ -1275,14 +1879,14 @@
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <f t="shared" si="1"/>
         <v>3780</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="17">
         <v>46290</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="17">
         <v>46307</v>
       </c>
       <c r="H24">
@@ -1300,29 +1904,29 @@
         <v>7500</v>
       </c>
       <c r="D25" s="3">
-        <f>B25*C25</f>
+        <f t="shared" si="0"/>
         <v>10500</v>
       </c>
-      <c r="E25" s="13">
-        <f>D25*0.9</f>
+      <c r="E25" s="12">
+        <f t="shared" si="1"/>
         <v>9450</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="18">
         <v>46302</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="18">
         <v>46317</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="4:5">
       <c r="D26" s="3">
         <f>SUM(D2:D25)</f>
         <v>128706</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <f>SUM(E2:E25)</f>
         <v>117402.4</v>
       </c>
@@ -1332,7 +1936,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C27" s="2">
         <v>30000</v>
@@ -1341,7 +1945,7 @@
         <f>B27*C27</f>
         <v>4200</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <f>D27*0.9</f>
         <v>3780</v>
       </c>
@@ -1359,18 +1963,18 @@
       <c r="A28" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="2">
         <f>C3+C27</f>
         <v>47500</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="20">
         <f>D3+D27</f>
         <v>5950</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="21">
         <f>E3+E27</f>
         <v>5355</v>
       </c>
@@ -1389,7 +1993,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C29" s="2">
         <v>55000</v>
@@ -1398,7 +2002,7 @@
         <f>B29*C29</f>
         <v>15400</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <f>D29*0.9</f>
         <v>13860</v>
       </c>
@@ -1417,7 +2021,7 @@
         <v>52</v>
       </c>
       <c r="B30" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C30" s="2">
         <v>24000</v>
@@ -1426,7 +2030,7 @@
         <f>B30*C30</f>
         <v>6720</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <f>D30*0.9</f>
         <v>6048</v>
       </c>
@@ -1440,23 +2044,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="2:5">
       <c r="B31"/>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <f>E29+E30</f>
         <v>19908</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="2:2">
       <c r="B32"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H23">
+  <sortState ref="A2:H23">
     <sortCondition ref="G2:G23"/>
     <sortCondition ref="A2:A23"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="D26" formula="1"/>
   </ignoredErrors>
@@ -1464,14 +2069,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="2"/>
     <col min="4" max="5" width="11" style="3" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" style="4" customWidth="1"/>
+    <col min="6" max="7" width="10.3333333333333" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1505,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C2" s="2">
         <v>120000</v>
@@ -1583,7 +2189,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="C5" s="2">
         <v>10000</v>
@@ -1661,7 +2267,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="C8" s="2">
         <v>55000</v>
@@ -1687,7 +2293,7 @@
         <v>29</v>
       </c>
       <c r="B9" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="C9" s="2">
         <v>45000</v>
@@ -1822,7 +2428,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="1">
-        <v>7.0499999999999993E-2</v>
+        <v>0.0705</v>
       </c>
       <c r="C14" s="2">
         <v>30000</v>
@@ -1850,7 +2456,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="C15" s="2">
         <v>30000</v>
@@ -1887,7 +2493,7 @@
         <f>B16*C16</f>
         <v>10500</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f>D16*0.9</f>
         <v>9450</v>
       </c>
@@ -2014,7 +2620,7 @@
       <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="13">
         <v>0.1133</v>
       </c>
       <c r="C21" s="2">
@@ -2142,7 +2748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="4:5">
       <c r="D26" s="3">
         <f>SUM(D2:D25)</f>
         <v>128706</v>
@@ -2153,10 +2759,11 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H25">
+  <sortState ref="A2:H25">
     <sortCondition ref="A2:A25"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>